--- a/db/fixtures/indexer.xlsx
+++ b/db/fixtures/indexer.xlsx
@@ -6,12 +6,13 @@
     <sheet name="2" sheetId="2" r:id="rId2"/>
     <sheet name="3" sheetId="3" r:id="rId3"/>
     <sheet name="МК" sheetId="4" r:id="rId4"/>
+    <sheet name="НП" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t>№ пп</t>
   </si>
@@ -371,6 +372,81 @@
   </si>
   <si>
     <t>умершего мать</t>
+  </si>
+  <si>
+    <t>Справочник населённых пунктов</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Тип</t>
+  </si>
+  <si>
+    <t>Губерния</t>
+  </si>
+  <si>
+    <t>Уезд</t>
+  </si>
+  <si>
+    <t>Волость</t>
+  </si>
+  <si>
+    <t>Кратко</t>
+  </si>
+  <si>
+    <t>Полностью</t>
+  </si>
+  <si>
+    <t>Familio</t>
+  </si>
+  <si>
+    <t>НП для ввода МК</t>
+  </si>
+  <si>
+    <t>д.</t>
+  </si>
+  <si>
+    <t>Тестовская</t>
+  </si>
+  <si>
+    <t>Тестовский</t>
+  </si>
+  <si>
+    <t>д. Тестово Малое</t>
+  </si>
+  <si>
+    <t>д. Тестово Малое, Тестовская волость, Тестовский уезд, Тестовская губерния</t>
+  </si>
+  <si>
+    <t>https://familio.org/settlements/00000000-0000-0000-0000-000000000001</t>
+  </si>
+  <si>
+    <t>с.</t>
+  </si>
+  <si>
+    <t>с. Верхнее Тестово</t>
+  </si>
+  <si>
+    <t>с. Верхнее Тестово, Тестовский уезд, Тестовская губерния</t>
+  </si>
+  <si>
+    <t>Дальнее Тестово</t>
+  </si>
+  <si>
+    <t>Соседний</t>
+  </si>
+  <si>
+    <t>Дальняя</t>
+  </si>
+  <si>
+    <t>д. Дальнее Тестово</t>
+  </si>
+  <si>
+    <t>д. Дальнее Тестово, Дальняя волость, Соседний уезд, Тестовская губерния</t>
+  </si>
+  <si>
+    <t>д.Дальнее Тестово, Дальняя волость</t>
   </si>
 </sst>
 </file>
@@ -1686,4 +1762,123 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5" t="s">
+        <v>143</v>
+      </c>
+      <c r="J5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>